--- a/stock-tri/market_breadth_tracker.xlsx
+++ b/stock-tri/market_breadth_tracker.xlsx
@@ -24872,7 +24872,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>© 2026 올투스탁랩 ALLTOO STOCK LAB  |  최근 업데이트: 2026-04-19</t>
+          <t>© 2026 올투스탁랩 ALLTOO STOCK LAB  |  최근 업데이트: 2026-04-20</t>
         </is>
       </c>
     </row>
